--- a/ig/ch-elm/ValueSet-ch-elm-results-hanta-org.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-hanta-org.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,28 +105,34 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>40754006</t>
+  </si>
+  <si>
+    <t>Puumala virus (organism)</t>
+  </si>
+  <si>
+    <t>116663002</t>
+  </si>
+  <si>
+    <t>Sin Nombre virus (organism)</t>
+  </si>
+  <si>
     <t>35439004</t>
   </si>
   <si>
     <t>Seoul virus (organism)</t>
   </si>
   <si>
-    <t>40754006</t>
-  </si>
-  <si>
-    <t>Puumala virus (organism)</t>
-  </si>
-  <si>
-    <t>116663002</t>
-  </si>
-  <si>
-    <t>Sin Nombre virus (organism)</t>
-  </si>
-  <si>
     <t>49445003</t>
   </si>
   <si>
     <t>Genus Hantavirus (organism)</t>
+  </si>
+  <si>
+    <t>442001008</t>
+  </si>
+  <si>
+    <t>Andes virus</t>
   </si>
   <si>
     <t>116662007</t>
@@ -454,50 +460,50 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/ig/ch-elm/ValueSet-ch-elm-results-hanta-org.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-hanta-org.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-hanta-org.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-hanta-org.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-hanta-org.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-hanta-org.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
